--- a/data/spieler.xlsx
+++ b/data/spieler.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bab6bfc8c781ef4f/fussballobmann/Touchmonitor/SV-Holtsee-Wittensee-Touch/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="44" documentId="8_{2AA08989-BC04-48B9-B1FC-85AF9B801E8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0DDF7230-ED1E-4729-8B2C-B0CC54075BAC}"/>
+  <xr:revisionPtr revIDLastSave="64" documentId="8_{2AA08989-BC04-48B9-B1FC-85AF9B801E8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2CFC79E0-612D-4DAA-9F40-EC4B730F630A}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{2F502BE3-C089-4694-AC90-61A97806A0B3}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{2F502BE3-C089-4694-AC90-61A97806A0B3}"/>
   </bookViews>
   <sheets>
     <sheet name="csv" sheetId="1" r:id="rId1"/>
@@ -32,20 +32,14 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="28">
   <si>
     <t>MF</t>
-  </si>
-  <si>
-    <t>maxi</t>
   </si>
   <si>
     <t>rot_zwoote</t>
@@ -123,22 +117,10 @@
     <t>erick</t>
   </si>
   <si>
-    <t>brice</t>
-  </si>
-  <si>
     <t>flo</t>
   </si>
   <si>
     <t>jonny</t>
-  </si>
-  <si>
-    <t>steffen</t>
-  </si>
-  <si>
-    <t>pauli</t>
-  </si>
-  <si>
-    <t>max</t>
   </si>
 </sst>
 </file>
@@ -217,8 +199,11 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Gesamt"/>
     </sheetNames>
@@ -226,16 +211,16 @@
       <sheetData sheetId="0">
         <row r="4">
           <cell r="B4" t="str">
-            <v>Alexander Schmidt</v>
+            <v>André Kaustrup</v>
           </cell>
           <cell r="C4">
-            <v>593</v>
+            <v>60</v>
           </cell>
           <cell r="D4">
             <v>0</v>
           </cell>
           <cell r="L4">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="M4">
             <v>0</v>
@@ -253,13 +238,13 @@
             <v>0</v>
           </cell>
           <cell r="U4">
-            <v>2</v>
+            <v>0</v>
           </cell>
           <cell r="V4">
             <v>0</v>
           </cell>
           <cell r="X4">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="Y4">
             <v>0</v>
@@ -267,13 +252,13 @@
         </row>
         <row r="5">
           <cell r="B5" t="str">
-            <v>André Kaustrup</v>
+            <v>Arne Brunkert</v>
           </cell>
           <cell r="C5">
-            <v>700</v>
+            <v>90</v>
           </cell>
           <cell r="D5">
-            <v>80</v>
+            <v>0</v>
           </cell>
           <cell r="L5">
             <v>0</v>
@@ -308,10 +293,10 @@
         </row>
         <row r="6">
           <cell r="B6" t="str">
-            <v>Arne Brunkert</v>
+            <v>Bjarne Wegner</v>
           </cell>
           <cell r="C6">
-            <v>789</v>
+            <v>0</v>
           </cell>
           <cell r="D6">
             <v>0</v>
@@ -349,19 +334,19 @@
         </row>
         <row r="7">
           <cell r="B7" t="str">
-            <v>Bent Sommer-Sievert</v>
+            <v>Bosse Kuhl</v>
           </cell>
           <cell r="C7">
             <v>0</v>
           </cell>
           <cell r="D7">
-            <v>90</v>
+            <v>75</v>
           </cell>
           <cell r="L7">
             <v>0</v>
           </cell>
           <cell r="M7">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="O7">
             <v>0</v>
@@ -390,16 +375,16 @@
         </row>
         <row r="8">
           <cell r="B8" t="str">
-            <v>Bjarne Wegner</v>
+            <v>Christoph Seibert</v>
           </cell>
           <cell r="C8">
-            <v>1113</v>
+            <v>90</v>
           </cell>
           <cell r="D8">
-            <v>60</v>
+            <v>0</v>
           </cell>
           <cell r="L8">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="M8">
             <v>0</v>
@@ -417,7 +402,7 @@
             <v>0</v>
           </cell>
           <cell r="U8">
-            <v>2</v>
+            <v>0</v>
           </cell>
           <cell r="V8">
             <v>0</v>
@@ -431,13 +416,13 @@
         </row>
         <row r="9">
           <cell r="B9" t="str">
-            <v>Bosse Kuhl</v>
+            <v>Emil Rux</v>
           </cell>
           <cell r="C9">
-            <v>60</v>
+            <v>0</v>
           </cell>
           <cell r="D9">
-            <v>1018</v>
+            <v>75</v>
           </cell>
           <cell r="L9">
             <v>0</v>
@@ -461,24 +446,24 @@
             <v>0</v>
           </cell>
           <cell r="V9">
-            <v>6</v>
+            <v>2</v>
           </cell>
           <cell r="X9">
             <v>0</v>
           </cell>
           <cell r="Y9">
-            <v>8</v>
+            <v>1</v>
           </cell>
         </row>
         <row r="10">
           <cell r="B10" t="str">
-            <v>Chris Hansen</v>
+            <v>Erick Ehlers</v>
           </cell>
           <cell r="C10">
-            <v>0</v>
+            <v>90</v>
           </cell>
           <cell r="D10">
-            <v>75</v>
+            <v>0</v>
           </cell>
           <cell r="L10">
             <v>0</v>
@@ -502,24 +487,24 @@
             <v>0</v>
           </cell>
           <cell r="V10">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="X10">
             <v>0</v>
           </cell>
           <cell r="Y10">
-            <v>1</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="11">
           <cell r="B11" t="str">
-            <v>Christian Schnitker</v>
+            <v>Erik Mohr</v>
           </cell>
           <cell r="C11">
             <v>0</v>
           </cell>
           <cell r="D11">
-            <v>170</v>
+            <v>90</v>
           </cell>
           <cell r="L11">
             <v>0</v>
@@ -543,7 +528,7 @@
             <v>0</v>
           </cell>
           <cell r="V11">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="X11">
             <v>0</v>
@@ -554,13 +539,13 @@
         </row>
         <row r="12">
           <cell r="B12" t="str">
-            <v>Christoph Seibert</v>
+            <v>Finn Paulinski</v>
           </cell>
           <cell r="C12">
-            <v>896</v>
+            <v>25</v>
           </cell>
           <cell r="D12">
-            <v>180</v>
+            <v>0</v>
           </cell>
           <cell r="L12">
             <v>1</v>
@@ -581,33 +566,33 @@
             <v>0</v>
           </cell>
           <cell r="U12">
-            <v>2</v>
+            <v>0</v>
           </cell>
           <cell r="V12">
             <v>0</v>
           </cell>
           <cell r="X12">
-            <v>2</v>
+            <v>0</v>
           </cell>
           <cell r="Y12">
-            <v>2</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="13">
           <cell r="B13" t="str">
-            <v>Erick Ehlers</v>
+            <v>Florian Höhndorf</v>
           </cell>
           <cell r="C13">
-            <v>1973</v>
+            <v>48</v>
           </cell>
           <cell r="D13">
-            <v>90</v>
+            <v>0</v>
           </cell>
           <cell r="L13">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="M13">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="O13">
             <v>0</v>
@@ -616,16 +601,16 @@
             <v>0</v>
           </cell>
           <cell r="R13">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="S13">
             <v>0</v>
           </cell>
           <cell r="U13">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="V13">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="X13">
             <v>0</v>
@@ -636,19 +621,19 @@
         </row>
         <row r="14">
           <cell r="B14" t="str">
-            <v>Erik Mohr</v>
+            <v>Hennes Makoben</v>
           </cell>
           <cell r="C14">
             <v>0</v>
           </cell>
           <cell r="D14">
-            <v>552</v>
+            <v>65</v>
           </cell>
           <cell r="L14">
             <v>0</v>
           </cell>
           <cell r="M14">
-            <v>2</v>
+            <v>0</v>
           </cell>
           <cell r="O14">
             <v>0</v>
@@ -677,13 +662,13 @@
         </row>
         <row r="15">
           <cell r="B15" t="str">
-            <v>Fabrice Christl</v>
+            <v>Jakob Rutscher</v>
           </cell>
           <cell r="C15">
             <v>0</v>
           </cell>
           <cell r="D15">
-            <v>1350</v>
+            <v>0</v>
           </cell>
           <cell r="L15">
             <v>0</v>
@@ -707,7 +692,7 @@
             <v>0</v>
           </cell>
           <cell r="V15">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="X15">
             <v>0</v>
@@ -718,16 +703,16 @@
         </row>
         <row r="16">
           <cell r="B16" t="str">
-            <v>Finn Paulinski</v>
+            <v>Jan-Emil Schäfer</v>
           </cell>
           <cell r="C16">
-            <v>740</v>
+            <v>90</v>
           </cell>
           <cell r="D16">
-            <v>600</v>
+            <v>0</v>
           </cell>
           <cell r="L16">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="M16">
             <v>0</v>
@@ -745,33 +730,33 @@
             <v>0</v>
           </cell>
           <cell r="U16">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="V16">
-            <v>4</v>
+            <v>0</v>
           </cell>
           <cell r="X16">
             <v>2</v>
           </cell>
           <cell r="Y16">
-            <v>2</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="17">
           <cell r="B17" t="str">
-            <v>Florian Höhndorf</v>
+            <v>Jannek Bahr</v>
           </cell>
           <cell r="C17">
-            <v>169</v>
+            <v>0</v>
           </cell>
           <cell r="D17">
-            <v>1615</v>
+            <v>0</v>
           </cell>
           <cell r="L17">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="M17">
-            <v>2</v>
+            <v>0</v>
           </cell>
           <cell r="O17">
             <v>0</v>
@@ -789,24 +774,24 @@
             <v>0</v>
           </cell>
           <cell r="V17">
-            <v>4</v>
+            <v>0</v>
           </cell>
           <cell r="X17">
             <v>0</v>
           </cell>
           <cell r="Y17">
-            <v>2</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="18">
           <cell r="B18" t="str">
-            <v>Hennes Makoben</v>
+            <v>Jannis Poerschke</v>
           </cell>
           <cell r="C18">
             <v>0</v>
           </cell>
           <cell r="D18">
-            <v>797</v>
+            <v>90</v>
           </cell>
           <cell r="L18">
             <v>0</v>
@@ -830,7 +815,7 @@
             <v>0</v>
           </cell>
           <cell r="V18">
-            <v>2</v>
+            <v>0</v>
           </cell>
           <cell r="X18">
             <v>0</v>
@@ -841,13 +826,13 @@
         </row>
         <row r="19">
           <cell r="B19" t="str">
-            <v>Jakob Rutscher</v>
+            <v>Jason Hannemann</v>
           </cell>
           <cell r="C19">
-            <v>225</v>
+            <v>0</v>
           </cell>
           <cell r="D19">
-            <v>270</v>
+            <v>25</v>
           </cell>
           <cell r="L19">
             <v>0</v>
@@ -874,24 +859,24 @@
             <v>0</v>
           </cell>
           <cell r="X19">
-            <v>2</v>
+            <v>0</v>
           </cell>
           <cell r="Y19">
-            <v>3</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="20">
           <cell r="B20" t="str">
-            <v>Jan-Emil Schäfer</v>
+            <v>Johann Jahn</v>
           </cell>
           <cell r="C20">
-            <v>1363</v>
+            <v>0</v>
           </cell>
           <cell r="D20">
             <v>0</v>
           </cell>
           <cell r="L20">
-            <v>6</v>
+            <v>0</v>
           </cell>
           <cell r="M20">
             <v>0</v>
@@ -909,13 +894,13 @@
             <v>0</v>
           </cell>
           <cell r="U20">
-            <v>2</v>
+            <v>0</v>
           </cell>
           <cell r="V20">
             <v>0</v>
           </cell>
           <cell r="X20">
-            <v>14</v>
+            <v>0</v>
           </cell>
           <cell r="Y20">
             <v>0</v>
@@ -923,25 +908,25 @@
         </row>
         <row r="21">
           <cell r="B21" t="str">
-            <v>Jannek Bahr</v>
+            <v>Jonas Vogel</v>
           </cell>
           <cell r="C21">
-            <v>270</v>
+            <v>0</v>
           </cell>
           <cell r="D21">
-            <v>131</v>
+            <v>45</v>
           </cell>
           <cell r="L21">
-            <v>2</v>
+            <v>0</v>
           </cell>
           <cell r="M21">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="O21">
             <v>0</v>
           </cell>
           <cell r="P21">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="R21">
             <v>0</v>
@@ -964,16 +949,16 @@
         </row>
         <row r="22">
           <cell r="B22" t="str">
-            <v>Jannis Poerschke</v>
+            <v>Justin Schink</v>
           </cell>
           <cell r="C22">
-            <v>752</v>
+            <v>0</v>
           </cell>
           <cell r="D22">
-            <v>90</v>
+            <v>0</v>
           </cell>
           <cell r="L22">
-            <v>4</v>
+            <v>0</v>
           </cell>
           <cell r="M22">
             <v>0</v>
@@ -991,7 +976,7 @@
             <v>0</v>
           </cell>
           <cell r="U22">
-            <v>2</v>
+            <v>0</v>
           </cell>
           <cell r="V22">
             <v>0</v>
@@ -1005,13 +990,13 @@
         </row>
         <row r="23">
           <cell r="B23" t="str">
-            <v>Johann Jahn</v>
+            <v>Kevin Bressler</v>
           </cell>
           <cell r="C23">
             <v>0</v>
           </cell>
           <cell r="D23">
-            <v>1059</v>
+            <v>0</v>
           </cell>
           <cell r="L23">
             <v>0</v>
@@ -1041,59 +1026,59 @@
             <v>0</v>
           </cell>
           <cell r="Y23">
-            <v>3</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="24">
           <cell r="B24" t="str">
-            <v>Jonas Vogel</v>
+            <v>Kevin Langbehn</v>
           </cell>
           <cell r="C24">
             <v>0</v>
           </cell>
           <cell r="D24">
-            <v>985</v>
+            <v>45</v>
           </cell>
           <cell r="L24">
             <v>0</v>
           </cell>
           <cell r="M24">
+            <v>0</v>
+          </cell>
+          <cell r="O24">
+            <v>0</v>
+          </cell>
+          <cell r="P24">
+            <v>0</v>
+          </cell>
+          <cell r="R24">
+            <v>0</v>
+          </cell>
+          <cell r="S24">
+            <v>0</v>
+          </cell>
+          <cell r="U24">
+            <v>0</v>
+          </cell>
+          <cell r="V24">
+            <v>2</v>
+          </cell>
+          <cell r="X24">
+            <v>0</v>
+          </cell>
+          <cell r="Y24">
             <v>1</v>
-          </cell>
-          <cell r="O24">
-            <v>0</v>
-          </cell>
-          <cell r="P24">
-            <v>0</v>
-          </cell>
-          <cell r="R24">
-            <v>0</v>
-          </cell>
-          <cell r="S24">
-            <v>0</v>
-          </cell>
-          <cell r="U24">
-            <v>0</v>
-          </cell>
-          <cell r="V24">
-            <v>4</v>
-          </cell>
-          <cell r="X24">
-            <v>0</v>
-          </cell>
-          <cell r="Y24">
-            <v>2</v>
           </cell>
         </row>
         <row r="25">
           <cell r="B25" t="str">
-            <v>Justin Schink</v>
+            <v>Kian Petersen</v>
           </cell>
           <cell r="C25">
-            <v>0</v>
+            <v>35</v>
           </cell>
           <cell r="D25">
-            <v>420</v>
+            <v>45</v>
           </cell>
           <cell r="L25">
             <v>0</v>
@@ -1117,24 +1102,24 @@
             <v>0</v>
           </cell>
           <cell r="V25">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="X25">
             <v>0</v>
           </cell>
           <cell r="Y25">
-            <v>0</v>
+            <v>1</v>
           </cell>
         </row>
         <row r="26">
           <cell r="B26" t="str">
-            <v>Kevin Bressler</v>
+            <v>Kjell Schröder</v>
           </cell>
           <cell r="C26">
-            <v>0</v>
+            <v>30</v>
           </cell>
           <cell r="D26">
-            <v>285</v>
+            <v>0</v>
           </cell>
           <cell r="L26">
             <v>0</v>
@@ -1155,7 +1140,7 @@
             <v>0</v>
           </cell>
           <cell r="U26">
-            <v>0</v>
+            <v>2</v>
           </cell>
           <cell r="V26">
             <v>0</v>
@@ -1169,57 +1154,57 @@
         </row>
         <row r="27">
           <cell r="B27" t="str">
-            <v>Kevin Langbehn</v>
+            <v>Lars Heinrich</v>
           </cell>
           <cell r="C27">
-            <v>1143</v>
+            <v>0</v>
           </cell>
           <cell r="D27">
-            <v>80</v>
+            <v>45</v>
           </cell>
           <cell r="L27">
-            <v>10</v>
+            <v>0</v>
           </cell>
           <cell r="M27">
             <v>0</v>
           </cell>
           <cell r="O27">
+            <v>0</v>
+          </cell>
+          <cell r="P27">
+            <v>0</v>
+          </cell>
+          <cell r="R27">
+            <v>0</v>
+          </cell>
+          <cell r="S27">
+            <v>0</v>
+          </cell>
+          <cell r="U27">
+            <v>0</v>
+          </cell>
+          <cell r="V27">
+            <v>0</v>
+          </cell>
+          <cell r="X27">
+            <v>0</v>
+          </cell>
+          <cell r="Y27">
             <v>1</v>
-          </cell>
-          <cell r="P27">
-            <v>0</v>
-          </cell>
-          <cell r="R27">
-            <v>0</v>
-          </cell>
-          <cell r="S27">
-            <v>0</v>
-          </cell>
-          <cell r="U27">
-            <v>7</v>
-          </cell>
-          <cell r="V27">
-            <v>0</v>
-          </cell>
-          <cell r="X27">
-            <v>8</v>
-          </cell>
-          <cell r="Y27">
-            <v>4</v>
           </cell>
         </row>
         <row r="28">
           <cell r="B28" t="str">
-            <v>Kian Petersen</v>
+            <v>Leon Blunck</v>
           </cell>
           <cell r="C28">
-            <v>1513</v>
+            <v>52</v>
           </cell>
           <cell r="D28">
             <v>0</v>
           </cell>
           <cell r="L28">
-            <v>3</v>
+            <v>0</v>
           </cell>
           <cell r="M28">
             <v>0</v>
@@ -1237,7 +1222,7 @@
             <v>0</v>
           </cell>
           <cell r="U28">
-            <v>7</v>
+            <v>0</v>
           </cell>
           <cell r="V28">
             <v>0</v>
@@ -1251,16 +1236,16 @@
         </row>
         <row r="29">
           <cell r="B29" t="str">
-            <v>Kjell Schröder</v>
+            <v>Lukas Koppe</v>
           </cell>
           <cell r="C29">
-            <v>146</v>
+            <v>0</v>
           </cell>
           <cell r="D29">
-            <v>290</v>
+            <v>0</v>
           </cell>
           <cell r="L29">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="M29">
             <v>0</v>
@@ -1281,24 +1266,24 @@
             <v>0</v>
           </cell>
           <cell r="V29">
-            <v>2</v>
+            <v>0</v>
           </cell>
           <cell r="X29">
             <v>0</v>
           </cell>
           <cell r="Y29">
-            <v>2</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="30">
           <cell r="B30" t="str">
-            <v>Lukas Koppe</v>
+            <v>Marcel Nass</v>
           </cell>
           <cell r="C30">
-            <v>323</v>
+            <v>90</v>
           </cell>
           <cell r="D30">
-            <v>595</v>
+            <v>0</v>
           </cell>
           <cell r="L30">
             <v>0</v>
@@ -1328,24 +1313,24 @@
             <v>0</v>
           </cell>
           <cell r="Y30">
-            <v>2</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="31">
           <cell r="B31" t="str">
-            <v>Maik Heisterkamp</v>
+            <v>Marek Stickelbruck</v>
           </cell>
           <cell r="C31">
-            <v>0</v>
+            <v>55</v>
           </cell>
           <cell r="D31">
-            <v>911</v>
+            <v>0</v>
           </cell>
           <cell r="L31">
             <v>0</v>
           </cell>
           <cell r="M31">
-            <v>3</v>
+            <v>0</v>
           </cell>
           <cell r="O31">
             <v>0</v>
@@ -1363,27 +1348,27 @@
             <v>0</v>
           </cell>
           <cell r="V31">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="X31">
             <v>0</v>
           </cell>
           <cell r="Y31">
-            <v>5</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="32">
           <cell r="B32" t="str">
-            <v>Marcel Nass</v>
+            <v>Markus Klamma</v>
           </cell>
           <cell r="C32">
-            <v>1826</v>
+            <v>30</v>
           </cell>
           <cell r="D32">
             <v>0</v>
           </cell>
           <cell r="L32">
-            <v>4</v>
+            <v>0</v>
           </cell>
           <cell r="M32">
             <v>0</v>
@@ -1415,13 +1400,13 @@
         </row>
         <row r="33">
           <cell r="B33" t="str">
-            <v>Marcel Sydow</v>
+            <v>Matti Bade</v>
           </cell>
           <cell r="C33">
             <v>0</v>
           </cell>
           <cell r="D33">
-            <v>149</v>
+            <v>70</v>
           </cell>
           <cell r="L33">
             <v>0</v>
@@ -1445,24 +1430,24 @@
             <v>0</v>
           </cell>
           <cell r="V33">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="X33">
             <v>0</v>
           </cell>
           <cell r="Y33">
-            <v>0</v>
+            <v>3</v>
           </cell>
         </row>
         <row r="34">
           <cell r="B34" t="str">
-            <v>Marek Stickelbruck</v>
+            <v>Max Rönnau</v>
           </cell>
           <cell r="C34">
-            <v>505</v>
+            <v>0</v>
           </cell>
           <cell r="D34">
-            <v>175</v>
+            <v>0</v>
           </cell>
           <cell r="L34">
             <v>0</v>
@@ -1486,27 +1471,27 @@
             <v>0</v>
           </cell>
           <cell r="V34">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="X34">
-            <v>3</v>
+            <v>0</v>
           </cell>
           <cell r="Y34">
-            <v>1</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="35">
           <cell r="B35" t="str">
-            <v>Matti Bade</v>
+            <v>Maximilian Schierholz</v>
           </cell>
           <cell r="C35">
-            <v>1439</v>
+            <v>0</v>
           </cell>
           <cell r="D35">
-            <v>90</v>
+            <v>0</v>
           </cell>
           <cell r="L35">
-            <v>9</v>
+            <v>0</v>
           </cell>
           <cell r="M35">
             <v>0</v>
@@ -1524,13 +1509,13 @@
             <v>0</v>
           </cell>
           <cell r="U35">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="V35">
             <v>0</v>
           </cell>
           <cell r="X35">
-            <v>7</v>
+            <v>0</v>
           </cell>
           <cell r="Y35">
             <v>0</v>
@@ -1538,16 +1523,16 @@
         </row>
         <row r="36">
           <cell r="B36" t="str">
-            <v>Max Laabs</v>
+            <v>Nicolas Wind</v>
           </cell>
           <cell r="C36">
-            <v>1200</v>
+            <v>0</v>
           </cell>
           <cell r="D36">
             <v>90</v>
           </cell>
           <cell r="L36">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="M36">
             <v>0</v>
@@ -1571,7 +1556,7 @@
             <v>0</v>
           </cell>
           <cell r="X36">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="Y36">
             <v>0</v>
@@ -1579,7 +1564,7 @@
         </row>
         <row r="37">
           <cell r="B37" t="str">
-            <v>Max Rönnau</v>
+            <v>Niklas Glück</v>
           </cell>
           <cell r="C37">
             <v>0</v>
@@ -1620,19 +1605,19 @@
         </row>
         <row r="38">
           <cell r="B38" t="str">
-            <v>Maximilian Pilz</v>
+            <v>Ole Ströh</v>
           </cell>
           <cell r="C38">
             <v>0</v>
           </cell>
           <cell r="D38">
-            <v>1358</v>
+            <v>0</v>
           </cell>
           <cell r="L38">
             <v>0</v>
           </cell>
           <cell r="M38">
-            <v>3</v>
+            <v>0</v>
           </cell>
           <cell r="O38">
             <v>0</v>
@@ -1650,30 +1635,30 @@
             <v>0</v>
           </cell>
           <cell r="V38">
-            <v>4</v>
+            <v>0</v>
           </cell>
           <cell r="X38">
             <v>0</v>
           </cell>
           <cell r="Y38">
-            <v>4</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="39">
           <cell r="B39" t="str">
-            <v>Nicolas Wind</v>
+            <v>Pascal Diedrichsen</v>
           </cell>
           <cell r="C39">
-            <v>99</v>
+            <v>90</v>
           </cell>
           <cell r="D39">
-            <v>1043</v>
+            <v>0</v>
           </cell>
           <cell r="L39">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="M39">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="O39">
             <v>0</v>
@@ -1691,27 +1676,27 @@
             <v>0</v>
           </cell>
           <cell r="V39">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="X39">
-            <v>0</v>
+            <v>2</v>
           </cell>
           <cell r="Y39">
-            <v>2</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="40">
           <cell r="B40" t="str">
-            <v>Niklas Glück</v>
+            <v>Philip Mahrt</v>
           </cell>
           <cell r="C40">
-            <v>1167</v>
+            <v>0</v>
           </cell>
           <cell r="D40">
             <v>0</v>
           </cell>
           <cell r="L40">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="M40">
             <v>0</v>
@@ -1735,7 +1720,7 @@
             <v>0</v>
           </cell>
           <cell r="X40">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="Y40">
             <v>0</v>
@@ -1743,16 +1728,16 @@
         </row>
         <row r="41">
           <cell r="B41" t="str">
-            <v>Ole Ströh</v>
+            <v>Philipp Röschmann</v>
           </cell>
           <cell r="C41">
-            <v>774</v>
+            <v>0</v>
           </cell>
           <cell r="D41">
-            <v>80</v>
+            <v>25</v>
           </cell>
           <cell r="L41">
-            <v>2</v>
+            <v>0</v>
           </cell>
           <cell r="M41">
             <v>0</v>
@@ -1770,24 +1755,24 @@
             <v>0</v>
           </cell>
           <cell r="U41">
+            <v>0</v>
+          </cell>
+          <cell r="V41">
+            <v>0</v>
+          </cell>
+          <cell r="X41">
+            <v>0</v>
+          </cell>
+          <cell r="Y41">
             <v>1</v>
-          </cell>
-          <cell r="V41">
-            <v>0</v>
-          </cell>
-          <cell r="X41">
-            <v>0</v>
-          </cell>
-          <cell r="Y41">
-            <v>0</v>
           </cell>
         </row>
         <row r="42">
           <cell r="B42" t="str">
-            <v>Roman Walter</v>
+            <v>Rouven Meister</v>
           </cell>
           <cell r="C42">
-            <v>0</v>
+            <v>75</v>
           </cell>
           <cell r="D42">
             <v>0</v>
@@ -1811,7 +1796,7 @@
             <v>0</v>
           </cell>
           <cell r="U42">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="V42">
             <v>0</v>
@@ -1825,16 +1810,16 @@
         </row>
         <row r="43">
           <cell r="B43" t="str">
-            <v>Rouven Meister</v>
+            <v>Sebastian Ehlers</v>
           </cell>
           <cell r="C43">
-            <v>1308</v>
+            <v>0</v>
           </cell>
           <cell r="D43">
-            <v>0</v>
+            <v>70</v>
           </cell>
           <cell r="L43">
-            <v>2</v>
+            <v>0</v>
           </cell>
           <cell r="M43">
             <v>0</v>
@@ -1852,13 +1837,13 @@
             <v>0</v>
           </cell>
           <cell r="U43">
+            <v>0</v>
+          </cell>
+          <cell r="V43">
             <v>1</v>
           </cell>
-          <cell r="V43">
-            <v>0</v>
-          </cell>
           <cell r="X43">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="Y43">
             <v>0</v>
@@ -1866,13 +1851,13 @@
         </row>
         <row r="44">
           <cell r="B44" t="str">
-            <v>Sebastian Ehlers</v>
+            <v>Sebastian Lange</v>
           </cell>
           <cell r="C44">
+            <v>0</v>
+          </cell>
+          <cell r="D44">
             <v>90</v>
-          </cell>
-          <cell r="D44">
-            <v>338</v>
           </cell>
           <cell r="L44">
             <v>0</v>
@@ -1907,19 +1892,19 @@
         </row>
         <row r="45">
           <cell r="B45" t="str">
-            <v>Sebastian Lange</v>
+            <v>Sebastian Röh</v>
           </cell>
           <cell r="C45">
-            <v>72</v>
+            <v>0</v>
           </cell>
           <cell r="D45">
-            <v>1800</v>
+            <v>0</v>
           </cell>
           <cell r="L45">
             <v>0</v>
           </cell>
           <cell r="M45">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="O45">
             <v>0</v>
@@ -1937,7 +1922,7 @@
             <v>0</v>
           </cell>
           <cell r="V45">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="X45">
             <v>0</v>
@@ -1948,13 +1933,13 @@
         </row>
         <row r="46">
           <cell r="B46" t="str">
-            <v>Sebastian Röh</v>
+            <v>Sebastian Saupe</v>
           </cell>
           <cell r="C46">
             <v>0</v>
           </cell>
           <cell r="D46">
-            <v>77</v>
+            <v>0</v>
           </cell>
           <cell r="L46">
             <v>0</v>
@@ -1989,13 +1974,13 @@
         </row>
         <row r="47">
           <cell r="B47" t="str">
-            <v>Sebastian Saupe</v>
+            <v>Simon Mathiesen</v>
           </cell>
           <cell r="C47">
             <v>0</v>
           </cell>
           <cell r="D47">
-            <v>560</v>
+            <v>0</v>
           </cell>
           <cell r="L47">
             <v>0</v>
@@ -2019,7 +2004,7 @@
             <v>0</v>
           </cell>
           <cell r="V47">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="X47">
             <v>0</v>
@@ -2030,13 +2015,13 @@
         </row>
         <row r="48">
           <cell r="B48" t="str">
-            <v>Simon Mathiesen</v>
+            <v>Steffen Zobott</v>
           </cell>
           <cell r="C48">
             <v>0</v>
           </cell>
           <cell r="D48">
-            <v>121</v>
+            <v>45</v>
           </cell>
           <cell r="L48">
             <v>0</v>
@@ -2060,30 +2045,30 @@
             <v>0</v>
           </cell>
           <cell r="V48">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="X48">
             <v>0</v>
           </cell>
           <cell r="Y48">
-            <v>1</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="49">
           <cell r="B49" t="str">
-            <v>Steffen Zobott</v>
+            <v>Tim Sachau</v>
           </cell>
           <cell r="C49">
-            <v>0</v>
+            <v>60</v>
           </cell>
           <cell r="D49">
-            <v>1551</v>
+            <v>0</v>
           </cell>
           <cell r="L49">
             <v>0</v>
           </cell>
           <cell r="M49">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="O49">
             <v>0</v>
@@ -2112,13 +2097,13 @@
         </row>
         <row r="50">
           <cell r="B50" t="str">
-            <v>Sven Köpernick</v>
+            <v>Tim-Peter Blunck</v>
           </cell>
           <cell r="C50">
             <v>0</v>
           </cell>
           <cell r="D50">
-            <v>90</v>
+            <v>0</v>
           </cell>
           <cell r="L50">
             <v>0</v>
@@ -2153,10 +2138,10 @@
         </row>
         <row r="51">
           <cell r="B51" t="str">
-            <v>Till Greiner-Hiero</v>
+            <v>Torge Bremer</v>
           </cell>
           <cell r="C51">
-            <v>517</v>
+            <v>0</v>
           </cell>
           <cell r="D51">
             <v>0</v>
@@ -2180,13 +2165,13 @@
             <v>0</v>
           </cell>
           <cell r="U51">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="V51">
             <v>0</v>
           </cell>
           <cell r="X51">
-            <v>3</v>
+            <v>0</v>
           </cell>
           <cell r="Y51">
             <v>0</v>
@@ -2194,16 +2179,16 @@
         </row>
         <row r="52">
           <cell r="B52" t="str">
-            <v>Tim Sachau</v>
+            <v>Veit Brücker</v>
           </cell>
           <cell r="C52">
-            <v>1710</v>
+            <v>0</v>
           </cell>
           <cell r="D52">
             <v>0</v>
           </cell>
           <cell r="L52">
-            <v>2</v>
+            <v>0</v>
           </cell>
           <cell r="M52">
             <v>0</v>
@@ -2235,19 +2220,19 @@
         </row>
         <row r="53">
           <cell r="B53" t="str">
-            <v>Tim Stratmann</v>
+            <v>Yannik Frahm</v>
           </cell>
           <cell r="C53">
             <v>0</v>
           </cell>
           <cell r="D53">
-            <v>420</v>
+            <v>0</v>
           </cell>
           <cell r="L53">
             <v>0</v>
           </cell>
           <cell r="M53">
-            <v>2</v>
+            <v>0</v>
           </cell>
           <cell r="O53">
             <v>0</v>
@@ -2271,18 +2256,18 @@
             <v>0</v>
           </cell>
           <cell r="Y53">
-            <v>1</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="54">
           <cell r="B54" t="str">
-            <v>Torge Bremer</v>
+            <v>Z1 Alexander Schrinner</v>
           </cell>
           <cell r="C54">
             <v>0</v>
           </cell>
           <cell r="D54">
-            <v>140</v>
+            <v>0</v>
           </cell>
           <cell r="L54">
             <v>0</v>
@@ -2317,13 +2302,13 @@
         </row>
         <row r="55">
           <cell r="B55" t="str">
-            <v>Veit Brücker</v>
+            <v>Z2 Mirco Maschevsky</v>
           </cell>
           <cell r="C55">
             <v>0</v>
           </cell>
           <cell r="D55">
-            <v>250</v>
+            <v>0</v>
           </cell>
           <cell r="L55">
             <v>0</v>
@@ -2347,7 +2332,7 @@
             <v>0</v>
           </cell>
           <cell r="V55">
-            <v>2</v>
+            <v>0</v>
           </cell>
           <cell r="X55">
             <v>0</v>
@@ -2358,19 +2343,19 @@
         </row>
         <row r="56">
           <cell r="B56" t="str">
-            <v>Z1 Joso Jochimsen</v>
+            <v>Z3 Dennis Witt</v>
           </cell>
           <cell r="C56">
             <v>0</v>
           </cell>
           <cell r="D56">
-            <v>198</v>
+            <v>0</v>
           </cell>
           <cell r="L56">
             <v>0</v>
           </cell>
           <cell r="M56">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="O56">
             <v>0</v>
@@ -2398,14 +2383,14 @@
           </cell>
         </row>
         <row r="57">
-          <cell r="B57" t="str">
-            <v>Z2 Lars Heinrich</v>
+          <cell r="B57">
+            <v>0</v>
           </cell>
           <cell r="C57">
             <v>0</v>
           </cell>
           <cell r="D57">
-            <v>209</v>
+            <v>0</v>
           </cell>
           <cell r="L57">
             <v>0</v>
@@ -2439,14 +2424,14 @@
           </cell>
         </row>
         <row r="58">
-          <cell r="B58" t="str">
-            <v>Z3 Jason Hannemann</v>
+          <cell r="B58">
+            <v>0</v>
           </cell>
           <cell r="C58">
             <v>0</v>
           </cell>
           <cell r="D58">
-            <v>49</v>
+            <v>0</v>
           </cell>
           <cell r="L58">
             <v>0</v>
@@ -2480,11 +2465,11 @@
           </cell>
         </row>
         <row r="59">
-          <cell r="B59" t="str">
-            <v>Z4 Pascal Diedrichsen</v>
+          <cell r="B59">
+            <v>0</v>
           </cell>
           <cell r="C59">
-            <v>333</v>
+            <v>0</v>
           </cell>
           <cell r="D59">
             <v>0</v>
@@ -2514,7 +2499,7 @@
             <v>0</v>
           </cell>
           <cell r="X59">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="Y59">
             <v>0</v>
@@ -2527,9 +2512,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022-Design">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 – 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2567,7 +2552,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 – 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2673,7 +2658,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 – 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2815,7 +2800,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2834,61 +2819,61 @@
   <sheetData>
     <row r="1" spans="1:17" ht="40.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:17" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B2" s="1" t="str">
         <f>[1]Gesamt!B4</f>
-        <v>Alexander Schmidt</v>
+        <v>André Kaustrup</v>
       </c>
       <c r="C2" s="1">
         <v>31</v>
@@ -2901,19 +2886,19 @@
       </c>
       <c r="F2" s="1">
         <f>[1]Gesamt!C4</f>
-        <v>593</v>
+        <v>60</v>
       </c>
       <c r="G2" s="1">
         <f>[1]Gesamt!X4</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" s="1">
         <f>[1]Gesamt!U4</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I2" s="1">
         <f>[1]Gesamt!L4</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" s="1">
         <f>[1]Gesamt!O4</f>
@@ -2951,20 +2936,20 @@
     <row r="3" spans="1:17" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B3" s="1" t="str">
         <f>[1]Gesamt!B5</f>
-        <v>André Kaustrup</v>
+        <v>Arne Brunkert</v>
       </c>
       <c r="C3" s="1">
         <v>5</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E3" s="2">
         <v>34513</v>
       </c>
       <c r="F3" s="1">
         <f>[1]Gesamt!C5</f>
-        <v>700</v>
+        <v>90</v>
       </c>
       <c r="G3" s="1">
         <f>[1]Gesamt!X5</f>
@@ -2988,7 +2973,7 @@
       </c>
       <c r="L3" s="1">
         <f>[1]Gesamt!D5</f>
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="M3" s="1">
         <f>[1]Gesamt!Y5</f>
@@ -3014,20 +2999,20 @@
     <row r="4" spans="1:17" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B4" s="1" t="str">
         <f>[1]Gesamt!B6</f>
-        <v>Arne Brunkert</v>
+        <v>Bjarne Wegner</v>
       </c>
       <c r="C4" s="1">
         <v>2</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E4" s="2">
         <v>42917</v>
       </c>
       <c r="F4" s="1">
         <f>[1]Gesamt!C6</f>
-        <v>789</v>
+        <v>0</v>
       </c>
       <c r="G4" s="1">
         <f>[1]Gesamt!X6</f>
@@ -3077,7 +3062,7 @@
     <row r="5" spans="1:17" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B5" s="1" t="str">
         <f>[1]Gesamt!B7</f>
-        <v>Bent Sommer-Sievert</v>
+        <v>Bosse Kuhl</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="1">
@@ -3106,7 +3091,7 @@
       </c>
       <c r="L5" s="1">
         <f>[1]Gesamt!D7</f>
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="M5" s="1">
         <f>[1]Gesamt!Y7</f>
@@ -3118,7 +3103,7 @@
       </c>
       <c r="O5" s="1">
         <f>[1]Gesamt!M7</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" s="1">
         <f>[1]Gesamt!P7</f>
@@ -3132,20 +3117,20 @@
     <row r="6" spans="1:17" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B6" s="1" t="str">
         <f>[1]Gesamt!B8</f>
-        <v>Bjarne Wegner</v>
+        <v>Christoph Seibert</v>
       </c>
       <c r="C6" s="1">
         <v>4</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E6" s="2">
         <v>42918</v>
       </c>
       <c r="F6" s="1">
         <f>[1]Gesamt!C8</f>
-        <v>1113</v>
+        <v>90</v>
       </c>
       <c r="G6" s="1">
         <f>[1]Gesamt!X8</f>
@@ -3153,11 +3138,11 @@
       </c>
       <c r="H6" s="1">
         <f>[1]Gesamt!U8</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I6" s="1">
         <f>[1]Gesamt!L8</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" s="1">
         <f>[1]Gesamt!O8</f>
@@ -3169,7 +3154,7 @@
       </c>
       <c r="L6" s="1">
         <f>[1]Gesamt!D8</f>
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="M6" s="1">
         <f>[1]Gesamt!Y8</f>
@@ -3195,20 +3180,20 @@
     <row r="7" spans="1:17" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B7" s="1" t="str">
         <f>[1]Gesamt!B9</f>
-        <v>Bosse Kuhl</v>
+        <v>Emil Rux</v>
       </c>
       <c r="C7" s="1">
         <v>23</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E7" s="2">
         <v>43484</v>
       </c>
       <c r="F7" s="1">
         <f>[1]Gesamt!C9</f>
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="G7" s="1">
         <f>[1]Gesamt!X9</f>
@@ -3232,15 +3217,15 @@
       </c>
       <c r="L7" s="1">
         <f>[1]Gesamt!D9</f>
-        <v>1018</v>
+        <v>75</v>
       </c>
       <c r="M7" s="1">
         <f>[1]Gesamt!Y9</f>
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="N7" s="1">
         <f>[1]Gesamt!V9</f>
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O7" s="1">
         <f>[1]Gesamt!M9</f>
@@ -3256,9 +3241,12 @@
       </c>
     </row>
     <row r="8" spans="1:17" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="B8" s="1" t="str">
         <f>[1]Gesamt!B10</f>
-        <v>Chris Hansen</v>
+        <v>Erick Ehlers</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>0</v>
@@ -3266,7 +3254,7 @@
       <c r="E8" s="2"/>
       <c r="F8" s="1">
         <f>[1]Gesamt!C10</f>
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="G8" s="1">
         <f>[1]Gesamt!X10</f>
@@ -3290,15 +3278,15 @@
       </c>
       <c r="L8" s="1">
         <f>[1]Gesamt!D10</f>
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="M8" s="1">
         <f>[1]Gesamt!Y10</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" s="1">
         <f>[1]Gesamt!V10</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" s="1">
         <f>[1]Gesamt!M10</f>
@@ -3316,10 +3304,10 @@
     <row r="9" spans="1:17" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B9" s="1" t="str">
         <f>[1]Gesamt!B11</f>
-        <v>Christian Schnitker</v>
+        <v>Erik Mohr</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="1">
@@ -3348,7 +3336,7 @@
       </c>
       <c r="L9" s="1">
         <f>[1]Gesamt!D11</f>
-        <v>170</v>
+        <v>90</v>
       </c>
       <c r="M9" s="1">
         <f>[1]Gesamt!Y11</f>
@@ -3356,7 +3344,7 @@
       </c>
       <c r="N9" s="1">
         <f>[1]Gesamt!V11</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O9" s="1">
         <f>[1]Gesamt!M11</f>
@@ -3374,7 +3362,7 @@
     <row r="10" spans="1:17" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B10" s="1" t="str">
         <f>[1]Gesamt!B12</f>
-        <v>Christoph Seibert</v>
+        <v>Finn Paulinski</v>
       </c>
       <c r="C10" s="1">
         <v>13</v>
@@ -3387,15 +3375,15 @@
       </c>
       <c r="F10" s="1">
         <f>[1]Gesamt!C12</f>
-        <v>896</v>
+        <v>25</v>
       </c>
       <c r="G10" s="1">
         <f>[1]Gesamt!X12</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H10" s="1">
         <f>[1]Gesamt!U12</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I10" s="1">
         <f>[1]Gesamt!L12</f>
@@ -3411,11 +3399,11 @@
       </c>
       <c r="L10" s="1">
         <f>[1]Gesamt!D12</f>
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="M10" s="1">
         <f>[1]Gesamt!Y12</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N10" s="1">
         <f>[1]Gesamt!V12</f>
@@ -3440,20 +3428,20 @@
       </c>
       <c r="B11" s="1" t="str">
         <f>[1]Gesamt!B13</f>
-        <v>Erick Ehlers</v>
+        <v>Florian Höhndorf</v>
       </c>
       <c r="C11" s="1">
         <v>27</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E11" s="2">
         <v>45474</v>
       </c>
       <c r="F11" s="1">
         <f>[1]Gesamt!C13</f>
-        <v>1973</v>
+        <v>48</v>
       </c>
       <c r="G11" s="1">
         <f>[1]Gesamt!X13</f>
@@ -3461,11 +3449,11 @@
       </c>
       <c r="H11" s="1">
         <f>[1]Gesamt!U13</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" s="1">
         <f>[1]Gesamt!L13</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" s="1">
         <f>[1]Gesamt!O13</f>
@@ -3473,11 +3461,11 @@
       </c>
       <c r="K11" s="1">
         <f>[1]Gesamt!R13</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" s="1">
         <f>[1]Gesamt!D13</f>
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="M11" s="1">
         <f>[1]Gesamt!Y13</f>
@@ -3485,11 +3473,11 @@
       </c>
       <c r="N11" s="1">
         <f>[1]Gesamt!V13</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11" s="1">
         <f>[1]Gesamt!M13</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P11" s="1">
         <f>[1]Gesamt!P13</f>
@@ -3503,13 +3491,13 @@
     <row r="12" spans="1:17" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B12" s="1" t="str">
         <f>[1]Gesamt!B14</f>
-        <v>Erik Mohr</v>
+        <v>Hennes Makoben</v>
       </c>
       <c r="C12" s="1">
         <v>1</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E12" s="2">
         <v>37825</v>
@@ -3540,7 +3528,7 @@
       </c>
       <c r="L12" s="1">
         <f>[1]Gesamt!D14</f>
-        <v>552</v>
+        <v>65</v>
       </c>
       <c r="M12" s="1">
         <f>[1]Gesamt!Y14</f>
@@ -3552,7 +3540,7 @@
       </c>
       <c r="O12" s="1">
         <f>[1]Gesamt!M14</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P12" s="1">
         <f>[1]Gesamt!P14</f>
@@ -3564,18 +3552,15 @@
       </c>
     </row>
     <row r="13" spans="1:17" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="B13" s="1" t="str">
         <f>[1]Gesamt!B15</f>
-        <v>Fabrice Christl</v>
+        <v>Jakob Rutscher</v>
       </c>
       <c r="C13" s="1">
         <v>1</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E13" s="2">
         <v>45732</v>
@@ -3606,7 +3591,7 @@
       </c>
       <c r="L13" s="1">
         <f>[1]Gesamt!D15</f>
-        <v>1350</v>
+        <v>0</v>
       </c>
       <c r="M13" s="1">
         <f>[1]Gesamt!Y15</f>
@@ -3614,7 +3599,7 @@
       </c>
       <c r="N13" s="1">
         <f>[1]Gesamt!V15</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O13" s="1">
         <f>[1]Gesamt!M15</f>
@@ -3630,12 +3615,9 @@
       </c>
     </row>
     <row r="14" spans="1:17" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="B14" s="1" t="str">
         <f>[1]Gesamt!B16</f>
-        <v>Finn Paulinski</v>
+        <v>Jan-Emil Schäfer</v>
       </c>
       <c r="C14" s="1">
         <v>10</v>
@@ -3648,7 +3630,7 @@
       </c>
       <c r="F14" s="1">
         <f>[1]Gesamt!C16</f>
-        <v>740</v>
+        <v>90</v>
       </c>
       <c r="G14" s="1">
         <f>[1]Gesamt!X16</f>
@@ -3656,11 +3638,11 @@
       </c>
       <c r="H14" s="1">
         <f>[1]Gesamt!U16</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14" s="1">
         <f>[1]Gesamt!L16</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14" s="1">
         <f>[1]Gesamt!O16</f>
@@ -3672,15 +3654,15 @@
       </c>
       <c r="L14" s="1">
         <f>[1]Gesamt!D16</f>
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="M14" s="1">
         <f>[1]Gesamt!Y16</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N14" s="1">
         <f>[1]Gesamt!V16</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O14" s="1">
         <f>[1]Gesamt!M16</f>
@@ -3696,25 +3678,22 @@
       </c>
     </row>
     <row r="15" spans="1:17" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="B15" s="1" t="str">
         <f>[1]Gesamt!B17</f>
-        <v>Florian Höhndorf</v>
+        <v>Jannek Bahr</v>
       </c>
       <c r="C15" s="1">
         <v>2</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E15" s="2">
         <v>45869</v>
       </c>
       <c r="F15" s="1">
         <f>[1]Gesamt!C17</f>
-        <v>169</v>
+        <v>0</v>
       </c>
       <c r="G15" s="1">
         <f>[1]Gesamt!X17</f>
@@ -3726,7 +3705,7 @@
       </c>
       <c r="I15" s="1">
         <f>[1]Gesamt!L17</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15" s="1">
         <f>[1]Gesamt!O17</f>
@@ -3738,19 +3717,19 @@
       </c>
       <c r="L15" s="1">
         <f>[1]Gesamt!D17</f>
-        <v>1615</v>
+        <v>0</v>
       </c>
       <c r="M15" s="1">
         <f>[1]Gesamt!Y17</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N15" s="1">
         <f>[1]Gesamt!V17</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O15" s="1">
         <f>[1]Gesamt!M17</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P15" s="1">
         <f>[1]Gesamt!P17</f>
@@ -3764,7 +3743,7 @@
     <row r="16" spans="1:17" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B16" s="1" t="str">
         <f>[1]Gesamt!B18</f>
-        <v>Hennes Makoben</v>
+        <v>Jannis Poerschke</v>
       </c>
       <c r="C16" s="1">
         <v>17</v>
@@ -3801,7 +3780,7 @@
       </c>
       <c r="L16" s="1">
         <f>[1]Gesamt!D18</f>
-        <v>797</v>
+        <v>90</v>
       </c>
       <c r="M16" s="1">
         <f>[1]Gesamt!Y18</f>
@@ -3809,7 +3788,7 @@
       </c>
       <c r="N16" s="1">
         <f>[1]Gesamt!V18</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O16" s="1">
         <f>[1]Gesamt!M18</f>
@@ -3827,24 +3806,24 @@
     <row r="17" spans="1:17" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B17" s="1" t="str">
         <f>[1]Gesamt!B19</f>
-        <v>Jakob Rutscher</v>
+        <v>Jason Hannemann</v>
       </c>
       <c r="C17" s="1">
         <v>5</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E17" s="2">
         <v>42006</v>
       </c>
       <c r="F17" s="1">
         <f>[1]Gesamt!C19</f>
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="G17" s="1">
         <f>[1]Gesamt!X19</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H17" s="1">
         <f>[1]Gesamt!U19</f>
@@ -3864,11 +3843,11 @@
       </c>
       <c r="L17" s="1">
         <f>[1]Gesamt!D19</f>
-        <v>270</v>
+        <v>25</v>
       </c>
       <c r="M17" s="1">
         <f>[1]Gesamt!Y19</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N17" s="1">
         <f>[1]Gesamt!V19</f>
@@ -3890,32 +3869,32 @@
     <row r="18" spans="1:17" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B18" s="1" t="str">
         <f>[1]Gesamt!B20</f>
-        <v>Jan-Emil Schäfer</v>
+        <v>Johann Jahn</v>
       </c>
       <c r="C18" s="1">
         <v>18</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E18" s="2">
         <v>45867</v>
       </c>
       <c r="F18" s="1">
         <f>[1]Gesamt!C20</f>
-        <v>1363</v>
+        <v>0</v>
       </c>
       <c r="G18" s="1">
         <f>[1]Gesamt!X20</f>
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H18" s="1">
         <f>[1]Gesamt!U20</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I18" s="1">
         <f>[1]Gesamt!L20</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J18" s="1">
         <f>[1]Gesamt!O20</f>
@@ -3951,22 +3930,25 @@
       </c>
     </row>
     <row r="19" spans="1:17" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A19" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="B19" s="1" t="str">
         <f>[1]Gesamt!B21</f>
-        <v>Jannek Bahr</v>
+        <v>Jonas Vogel</v>
       </c>
       <c r="C19" s="1">
         <v>44</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E19" s="2">
         <v>38134</v>
       </c>
       <c r="F19" s="1">
         <f>[1]Gesamt!C21</f>
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="G19" s="1">
         <f>[1]Gesamt!X21</f>
@@ -3978,7 +3960,7 @@
       </c>
       <c r="I19" s="1">
         <f>[1]Gesamt!L21</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J19" s="1">
         <f>[1]Gesamt!O21</f>
@@ -3990,7 +3972,7 @@
       </c>
       <c r="L19" s="1">
         <f>[1]Gesamt!D21</f>
-        <v>131</v>
+        <v>45</v>
       </c>
       <c r="M19" s="1">
         <f>[1]Gesamt!Y21</f>
@@ -4002,11 +3984,11 @@
       </c>
       <c r="O19" s="1">
         <f>[1]Gesamt!M21</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P19" s="1">
         <f>[1]Gesamt!P21</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q19" s="1">
         <f>[1]Gesamt!S21</f>
@@ -4016,7 +3998,7 @@
     <row r="20" spans="1:17" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B20" s="1" t="str">
         <f>[1]Gesamt!B22</f>
-        <v>Jannis Poerschke</v>
+        <v>Justin Schink</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>0</v>
@@ -4026,7 +4008,7 @@
       </c>
       <c r="F20" s="1">
         <f>[1]Gesamt!C22</f>
-        <v>752</v>
+        <v>0</v>
       </c>
       <c r="G20" s="1">
         <f>[1]Gesamt!X22</f>
@@ -4034,11 +4016,11 @@
       </c>
       <c r="H20" s="1">
         <f>[1]Gesamt!U22</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I20" s="1">
         <f>[1]Gesamt!L22</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J20" s="1">
         <f>[1]Gesamt!O22</f>
@@ -4050,7 +4032,7 @@
       </c>
       <c r="L20" s="1">
         <f>[1]Gesamt!D22</f>
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="M20" s="1">
         <f>[1]Gesamt!Y22</f>
@@ -4076,10 +4058,10 @@
     <row r="21" spans="1:17" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B21" s="1" t="str">
         <f>[1]Gesamt!B23</f>
-        <v>Johann Jahn</v>
+        <v>Kevin Bressler</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E21" s="2">
         <v>45870</v>
@@ -4110,11 +4092,11 @@
       </c>
       <c r="L21" s="1">
         <f>[1]Gesamt!D23</f>
-        <v>1059</v>
+        <v>0</v>
       </c>
       <c r="M21" s="1">
         <f>[1]Gesamt!Y23</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N21" s="1">
         <f>[1]Gesamt!V23</f>
@@ -4135,11 +4117,11 @@
     </row>
     <row r="22" spans="1:17" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B22" s="1" t="str">
         <f>[1]Gesamt!B24</f>
-        <v>Jonas Vogel</v>
+        <v>Kevin Langbehn</v>
       </c>
       <c r="C22" s="1">
         <v>7</v>
@@ -4176,19 +4158,19 @@
       </c>
       <c r="L22" s="1">
         <f>[1]Gesamt!D24</f>
-        <v>985</v>
+        <v>45</v>
       </c>
       <c r="M22" s="1">
         <f>[1]Gesamt!Y24</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N22" s="1">
         <f>[1]Gesamt!V24</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O22" s="1">
         <f>[1]Gesamt!M24</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P22" s="1">
         <f>[1]Gesamt!P24</f>
@@ -4202,20 +4184,20 @@
     <row r="23" spans="1:17" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B23" s="1" t="str">
         <f>[1]Gesamt!B25</f>
-        <v>Justin Schink</v>
+        <v>Kian Petersen</v>
       </c>
       <c r="C23" s="1">
         <v>11</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E23" s="2">
         <v>39787</v>
       </c>
       <c r="F23" s="1">
         <f>[1]Gesamt!C25</f>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G23" s="1">
         <f>[1]Gesamt!X25</f>
@@ -4239,15 +4221,15 @@
       </c>
       <c r="L23" s="1">
         <f>[1]Gesamt!D25</f>
-        <v>420</v>
+        <v>45</v>
       </c>
       <c r="M23" s="1">
         <f>[1]Gesamt!Y25</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N23" s="1">
         <f>[1]Gesamt!V25</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O23" s="1">
         <f>[1]Gesamt!M25</f>
@@ -4265,7 +4247,7 @@
     <row r="24" spans="1:17" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B24" s="1" t="str">
         <f>[1]Gesamt!B26</f>
-        <v>Kevin Bressler</v>
+        <v>Kjell Schröder</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>0</v>
@@ -4275,7 +4257,7 @@
       </c>
       <c r="F24" s="1">
         <f>[1]Gesamt!C26</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G24" s="1">
         <f>[1]Gesamt!X26</f>
@@ -4283,7 +4265,7 @@
       </c>
       <c r="H24" s="1">
         <f>[1]Gesamt!U26</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I24" s="1">
         <f>[1]Gesamt!L26</f>
@@ -4299,7 +4281,7 @@
       </c>
       <c r="L24" s="1">
         <f>[1]Gesamt!D26</f>
-        <v>285</v>
+        <v>0</v>
       </c>
       <c r="M24" s="1">
         <f>[1]Gesamt!Y26</f>
@@ -4323,41 +4305,38 @@
       </c>
     </row>
     <row r="25" spans="1:17" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="B25" s="1" t="str">
         <f>[1]Gesamt!B27</f>
-        <v>Kevin Langbehn</v>
+        <v>Lars Heinrich</v>
       </c>
       <c r="C25" s="1">
         <v>22</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E25" s="2">
         <v>45303</v>
       </c>
       <c r="F25" s="1">
         <f>[1]Gesamt!C27</f>
-        <v>1143</v>
+        <v>0</v>
       </c>
       <c r="G25" s="1">
         <f>[1]Gesamt!X27</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H25" s="1">
         <f>[1]Gesamt!U27</f>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I25" s="1">
         <f>[1]Gesamt!L27</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J25" s="1">
         <f>[1]Gesamt!O27</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" s="1">
         <f>[1]Gesamt!R27</f>
@@ -4365,11 +4344,11 @@
       </c>
       <c r="L25" s="1">
         <f>[1]Gesamt!D27</f>
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="M25" s="1">
         <f>[1]Gesamt!Y27</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N25" s="1">
         <f>[1]Gesamt!V27</f>
@@ -4391,7 +4370,7 @@
     <row r="26" spans="1:17" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B26" s="1" t="str">
         <f>[1]Gesamt!B28</f>
-        <v>Kian Petersen</v>
+        <v>Leon Blunck</v>
       </c>
       <c r="C26" s="1">
         <v>11</v>
@@ -4404,7 +4383,7 @@
       </c>
       <c r="F26" s="1">
         <f>[1]Gesamt!C28</f>
-        <v>1513</v>
+        <v>52</v>
       </c>
       <c r="G26" s="1">
         <f>[1]Gesamt!X28</f>
@@ -4412,11 +4391,11 @@
       </c>
       <c r="H26" s="1">
         <f>[1]Gesamt!U28</f>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I26" s="1">
         <f>[1]Gesamt!L28</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J26" s="1">
         <f>[1]Gesamt!O28</f>
@@ -4454,7 +4433,7 @@
     <row r="27" spans="1:17" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B27" s="1" t="str">
         <f>[1]Gesamt!B29</f>
-        <v>Kjell Schröder</v>
+        <v>Lukas Koppe</v>
       </c>
       <c r="C27" s="1">
         <v>19</v>
@@ -4467,7 +4446,7 @@
       </c>
       <c r="F27" s="1">
         <f>[1]Gesamt!C29</f>
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="G27" s="1">
         <f>[1]Gesamt!X29</f>
@@ -4479,7 +4458,7 @@
       </c>
       <c r="I27" s="1">
         <f>[1]Gesamt!L29</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J27" s="1">
         <f>[1]Gesamt!O29</f>
@@ -4491,15 +4470,15 @@
       </c>
       <c r="L27" s="1">
         <f>[1]Gesamt!D29</f>
-        <v>290</v>
+        <v>0</v>
       </c>
       <c r="M27" s="1">
         <f>[1]Gesamt!Y29</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N27" s="1">
         <f>[1]Gesamt!V29</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O27" s="1">
         <f>[1]Gesamt!M29</f>
@@ -4515,22 +4494,25 @@
       </c>
     </row>
     <row r="28" spans="1:17" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A28" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="B28" s="1" t="str">
         <f>[1]Gesamt!B30</f>
-        <v>Lukas Koppe</v>
+        <v>Marcel Nass</v>
       </c>
       <c r="C28" s="1">
         <v>22</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E28" s="2">
         <v>45350</v>
       </c>
       <c r="F28" s="1">
         <f>[1]Gesamt!C30</f>
-        <v>323</v>
+        <v>90</v>
       </c>
       <c r="G28" s="1">
         <f>[1]Gesamt!X30</f>
@@ -4554,11 +4536,11 @@
       </c>
       <c r="L28" s="1">
         <f>[1]Gesamt!D30</f>
-        <v>595</v>
+        <v>0</v>
       </c>
       <c r="M28" s="1">
         <f>[1]Gesamt!Y30</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N28" s="1">
         <f>[1]Gesamt!V30</f>
@@ -4580,7 +4562,7 @@
     <row r="29" spans="1:17" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B29" s="1" t="str">
         <f>[1]Gesamt!B31</f>
-        <v>Maik Heisterkamp</v>
+        <v>Marek Stickelbruck</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>0</v>
@@ -4588,7 +4570,7 @@
       <c r="E29" s="2"/>
       <c r="F29" s="1">
         <f>[1]Gesamt!C31</f>
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="G29" s="1">
         <f>[1]Gesamt!X31</f>
@@ -4612,19 +4594,19 @@
       </c>
       <c r="L29" s="1">
         <f>[1]Gesamt!D31</f>
-        <v>911</v>
+        <v>0</v>
       </c>
       <c r="M29" s="1">
         <f>[1]Gesamt!Y31</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N29" s="1">
         <f>[1]Gesamt!V31</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O29" s="1">
         <f>[1]Gesamt!M31</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P29" s="1">
         <f>[1]Gesamt!P31</f>
@@ -4636,12 +4618,9 @@
       </c>
     </row>
     <row r="30" spans="1:17" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="B30" s="1" t="str">
         <f>[1]Gesamt!B32</f>
-        <v>Marcel Nass</v>
+        <v>Markus Klamma</v>
       </c>
       <c r="C30" s="1">
         <v>6</v>
@@ -4654,7 +4633,7 @@
       </c>
       <c r="F30" s="1">
         <f>[1]Gesamt!C32</f>
-        <v>1826</v>
+        <v>30</v>
       </c>
       <c r="G30" s="1">
         <f>[1]Gesamt!X32</f>
@@ -4666,7 +4645,7 @@
       </c>
       <c r="I30" s="1">
         <f>[1]Gesamt!L32</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J30" s="1">
         <f>[1]Gesamt!O32</f>
@@ -4704,7 +4683,7 @@
     <row r="31" spans="1:17" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B31" s="1" t="str">
         <f>[1]Gesamt!B33</f>
-        <v>Marcel Sydow</v>
+        <v>Matti Bade</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" s="1">
@@ -4733,15 +4712,15 @@
       </c>
       <c r="L31" s="1">
         <f>[1]Gesamt!D33</f>
-        <v>149</v>
+        <v>70</v>
       </c>
       <c r="M31" s="1">
         <f>[1]Gesamt!Y33</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N31" s="1">
         <f>[1]Gesamt!V33</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O31" s="1">
         <f>[1]Gesamt!M33</f>
@@ -4759,24 +4738,24 @@
     <row r="32" spans="1:17" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B32" s="1" t="str">
         <f>[1]Gesamt!B34</f>
-        <v>Marek Stickelbruck</v>
+        <v>Max Rönnau</v>
       </c>
       <c r="C32" s="1">
         <v>21</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E32" s="2">
         <v>45839</v>
       </c>
       <c r="F32" s="1">
         <f>[1]Gesamt!C34</f>
-        <v>505</v>
+        <v>0</v>
       </c>
       <c r="G32" s="1">
         <f>[1]Gesamt!X34</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H32" s="1">
         <f>[1]Gesamt!U34</f>
@@ -4796,15 +4775,15 @@
       </c>
       <c r="L32" s="1">
         <f>[1]Gesamt!D34</f>
-        <v>175</v>
+        <v>0</v>
       </c>
       <c r="M32" s="1">
         <f>[1]Gesamt!Y34</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N32" s="1">
         <f>[1]Gesamt!V34</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O32" s="1">
         <f>[1]Gesamt!M34</f>
@@ -4822,32 +4801,32 @@
     <row r="33" spans="1:17" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B33" s="1" t="str">
         <f>[1]Gesamt!B35</f>
-        <v>Matti Bade</v>
+        <v>Maximilian Schierholz</v>
       </c>
       <c r="C33" s="1">
         <v>9</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E33" s="2">
         <v>45477</v>
       </c>
       <c r="F33" s="1">
         <f>[1]Gesamt!C35</f>
-        <v>1439</v>
+        <v>0</v>
       </c>
       <c r="G33" s="1">
         <f>[1]Gesamt!X35</f>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H33" s="1">
         <f>[1]Gesamt!U35</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I33" s="1">
         <f>[1]Gesamt!L35</f>
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J33" s="1">
         <f>[1]Gesamt!O35</f>
@@ -4859,7 +4838,7 @@
       </c>
       <c r="L33" s="1">
         <f>[1]Gesamt!D35</f>
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="M33" s="1">
         <f>[1]Gesamt!Y35</f>
@@ -4883,29 +4862,26 @@
       </c>
     </row>
     <row r="34" spans="1:17" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="B34" s="1" t="str">
         <f>[1]Gesamt!B36</f>
-        <v>Max Laabs</v>
+        <v>Nicolas Wind</v>
       </c>
       <c r="C34" s="1">
         <v>7</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E34" s="2">
         <v>37127</v>
       </c>
       <c r="F34" s="1">
         <f>[1]Gesamt!C36</f>
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="G34" s="1">
         <f>[1]Gesamt!X36</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H34" s="1">
         <f>[1]Gesamt!U36</f>
@@ -4913,7 +4889,7 @@
       </c>
       <c r="I34" s="1">
         <f>[1]Gesamt!L36</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J34" s="1">
         <f>[1]Gesamt!O36</f>
@@ -4951,7 +4927,7 @@
     <row r="35" spans="1:17" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B35" s="1" t="str">
         <f>[1]Gesamt!B37</f>
-        <v>Max Rönnau</v>
+        <v>Niklas Glück</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>0</v>
@@ -5007,12 +4983,9 @@
       </c>
     </row>
     <row r="36" spans="1:17" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="B36" s="1" t="str">
         <f>[1]Gesamt!B38</f>
-        <v>Maximilian Pilz</v>
+        <v>Ole Ströh</v>
       </c>
       <c r="C36" s="1">
         <v>6</v>
@@ -5049,19 +5022,19 @@
       </c>
       <c r="L36" s="1">
         <f>[1]Gesamt!D38</f>
-        <v>1358</v>
+        <v>0</v>
       </c>
       <c r="M36" s="1">
         <f>[1]Gesamt!Y38</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N36" s="1">
         <f>[1]Gesamt!V38</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O36" s="1">
         <f>[1]Gesamt!M38</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P36" s="1">
         <f>[1]Gesamt!P38</f>
@@ -5075,24 +5048,24 @@
     <row r="37" spans="1:17" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B37" s="1" t="str">
         <f>[1]Gesamt!B39</f>
-        <v>Nicolas Wind</v>
+        <v>Pascal Diedrichsen</v>
       </c>
       <c r="C37" s="1">
         <v>4</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E37" s="2">
         <v>43605</v>
       </c>
       <c r="F37" s="1">
         <f>[1]Gesamt!C39</f>
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="G37" s="1">
         <f>[1]Gesamt!X39</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H37" s="1">
         <f>[1]Gesamt!U39</f>
@@ -5100,7 +5073,7 @@
       </c>
       <c r="I37" s="1">
         <f>[1]Gesamt!L39</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J37" s="1">
         <f>[1]Gesamt!O39</f>
@@ -5112,19 +5085,19 @@
       </c>
       <c r="L37" s="1">
         <f>[1]Gesamt!D39</f>
-        <v>1043</v>
+        <v>0</v>
       </c>
       <c r="M37" s="1">
         <f>[1]Gesamt!Y39</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N37" s="1">
         <f>[1]Gesamt!V39</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O37" s="1">
         <f>[1]Gesamt!M39</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P37" s="1">
         <f>[1]Gesamt!P39</f>
@@ -5138,24 +5111,24 @@
     <row r="38" spans="1:17" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B38" s="1" t="str">
         <f>[1]Gesamt!B40</f>
-        <v>Niklas Glück</v>
+        <v>Philip Mahrt</v>
       </c>
       <c r="C38" s="1">
         <v>2</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E38" s="2">
         <v>41877</v>
       </c>
       <c r="F38" s="1">
         <f>[1]Gesamt!C40</f>
-        <v>1167</v>
+        <v>0</v>
       </c>
       <c r="G38" s="1">
         <f>[1]Gesamt!X40</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H38" s="1">
         <f>[1]Gesamt!U40</f>
@@ -5163,7 +5136,7 @@
       </c>
       <c r="I38" s="1">
         <f>[1]Gesamt!L40</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J38" s="1">
         <f>[1]Gesamt!O40</f>
@@ -5201,7 +5174,7 @@
     <row r="39" spans="1:17" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B39" s="1" t="str">
         <f>[1]Gesamt!B41</f>
-        <v>Ole Ströh</v>
+        <v>Philipp Röschmann</v>
       </c>
       <c r="C39" s="1">
         <v>17</v>
@@ -5214,7 +5187,7 @@
       </c>
       <c r="F39" s="1">
         <f>[1]Gesamt!C41</f>
-        <v>774</v>
+        <v>0</v>
       </c>
       <c r="G39" s="1">
         <f>[1]Gesamt!X41</f>
@@ -5222,11 +5195,11 @@
       </c>
       <c r="H39" s="1">
         <f>[1]Gesamt!U41</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I39" s="1">
         <f>[1]Gesamt!L41</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J39" s="1">
         <f>[1]Gesamt!O41</f>
@@ -5238,11 +5211,11 @@
       </c>
       <c r="L39" s="1">
         <f>[1]Gesamt!D41</f>
-        <v>80</v>
+        <v>25</v>
       </c>
       <c r="M39" s="1">
         <f>[1]Gesamt!Y41</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N39" s="1">
         <f>[1]Gesamt!V41</f>
@@ -5264,12 +5237,12 @@
     <row r="40" spans="1:17" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B40" s="1" t="str">
         <f>[1]Gesamt!B42</f>
-        <v>Roman Walter</v>
+        <v>Rouven Meister</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" s="1">
         <f>[1]Gesamt!C42</f>
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G40" s="1">
         <f>[1]Gesamt!X42</f>
@@ -5277,7 +5250,7 @@
       </c>
       <c r="H40" s="1">
         <f>[1]Gesamt!U42</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I40" s="1">
         <f>[1]Gesamt!L42</f>
@@ -5319,7 +5292,7 @@
     <row r="41" spans="1:17" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B41" s="1" t="str">
         <f>[1]Gesamt!B43</f>
-        <v>Rouven Meister</v>
+        <v>Sebastian Ehlers</v>
       </c>
       <c r="C41" s="1">
         <v>8</v>
@@ -5332,19 +5305,19 @@
       </c>
       <c r="F41" s="1">
         <f>[1]Gesamt!C43</f>
-        <v>1308</v>
+        <v>0</v>
       </c>
       <c r="G41" s="1">
         <f>[1]Gesamt!X43</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H41" s="1">
         <f>[1]Gesamt!U43</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I41" s="1">
         <f>[1]Gesamt!L43</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J41" s="1">
         <f>[1]Gesamt!O43</f>
@@ -5356,7 +5329,7 @@
       </c>
       <c r="L41" s="1">
         <f>[1]Gesamt!D43</f>
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="M41" s="1">
         <f>[1]Gesamt!Y43</f>
@@ -5364,7 +5337,7 @@
       </c>
       <c r="N41" s="1">
         <f>[1]Gesamt!V43</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O41" s="1">
         <f>[1]Gesamt!M43</f>
@@ -5380,9 +5353,12 @@
       </c>
     </row>
     <row r="42" spans="1:17" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A42" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="B42" s="1" t="str">
         <f>[1]Gesamt!B44</f>
-        <v>Sebastian Ehlers</v>
+        <v>Sebastian Lange</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>0</v>
@@ -5392,7 +5368,7 @@
       </c>
       <c r="F42" s="1">
         <f>[1]Gesamt!C44</f>
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="G42" s="1">
         <f>[1]Gesamt!X44</f>
@@ -5416,7 +5392,7 @@
       </c>
       <c r="L42" s="1">
         <f>[1]Gesamt!D44</f>
-        <v>338</v>
+        <v>90</v>
       </c>
       <c r="M42" s="1">
         <f>[1]Gesamt!Y44</f>
@@ -5440,25 +5416,22 @@
       </c>
     </row>
     <row r="43" spans="1:17" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A43" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="B43" s="1" t="str">
         <f>[1]Gesamt!B45</f>
-        <v>Sebastian Lange</v>
+        <v>Sebastian Röh</v>
       </c>
       <c r="C43" s="1">
         <v>18</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E43" s="2">
         <v>44943</v>
       </c>
       <c r="F43" s="1">
         <f>[1]Gesamt!C45</f>
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="G43" s="1">
         <f>[1]Gesamt!X45</f>
@@ -5482,7 +5455,7 @@
       </c>
       <c r="L43" s="1">
         <f>[1]Gesamt!D45</f>
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="M43" s="1">
         <f>[1]Gesamt!Y45</f>
@@ -5490,11 +5463,11 @@
       </c>
       <c r="N43" s="1">
         <f>[1]Gesamt!V45</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O43" s="1">
         <f>[1]Gesamt!M45</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P43" s="1">
         <f>[1]Gesamt!P45</f>
@@ -5508,10 +5481,10 @@
     <row r="44" spans="1:17" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B44" s="1" t="str">
         <f>[1]Gesamt!B46</f>
-        <v>Sebastian Röh</v>
+        <v>Sebastian Saupe</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E44" s="2">
         <v>44067</v>
@@ -5542,7 +5515,7 @@
       </c>
       <c r="L44" s="1">
         <f>[1]Gesamt!D46</f>
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="M44" s="1">
         <f>[1]Gesamt!Y46</f>
@@ -5568,10 +5541,10 @@
     <row r="45" spans="1:17" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B45" s="1" t="str">
         <f>[1]Gesamt!B47</f>
-        <v>Sebastian Saupe</v>
+        <v>Simon Mathiesen</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E45" s="2">
         <v>40544</v>
@@ -5602,7 +5575,7 @@
       </c>
       <c r="L45" s="1">
         <f>[1]Gesamt!D47</f>
-        <v>560</v>
+        <v>0</v>
       </c>
       <c r="M45" s="1">
         <f>[1]Gesamt!Y47</f>
@@ -5610,7 +5583,7 @@
       </c>
       <c r="N45" s="1">
         <f>[1]Gesamt!V47</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O45" s="1">
         <f>[1]Gesamt!M47</f>
@@ -5628,7 +5601,7 @@
     <row r="46" spans="1:17" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B46" s="1" t="str">
         <f>[1]Gesamt!B48</f>
-        <v>Simon Mathiesen</v>
+        <v>Steffen Zobott</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" s="1">
@@ -5657,15 +5630,15 @@
       </c>
       <c r="L46" s="1">
         <f>[1]Gesamt!D48</f>
-        <v>121</v>
+        <v>45</v>
       </c>
       <c r="M46" s="1">
         <f>[1]Gesamt!Y48</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N46" s="1">
         <f>[1]Gesamt!V48</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O46" s="1">
         <f>[1]Gesamt!M48</f>
@@ -5682,24 +5655,24 @@
     </row>
     <row r="47" spans="1:17" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A47" s="1" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="B47" s="1" t="str">
         <f>[1]Gesamt!B49</f>
-        <v>Steffen Zobott</v>
+        <v>Tim Sachau</v>
       </c>
       <c r="C47" s="1">
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E47" s="2">
         <v>43374</v>
       </c>
       <c r="F47" s="1">
         <f>[1]Gesamt!C49</f>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G47" s="1">
         <f>[1]Gesamt!X49</f>
@@ -5723,7 +5696,7 @@
       </c>
       <c r="L47" s="1">
         <f>[1]Gesamt!D49</f>
-        <v>1551</v>
+        <v>0</v>
       </c>
       <c r="M47" s="1">
         <f>[1]Gesamt!Y49</f>
@@ -5735,7 +5708,7 @@
       </c>
       <c r="O47" s="1">
         <f>[1]Gesamt!M49</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P47" s="1">
         <f>[1]Gesamt!P49</f>
@@ -5749,7 +5722,7 @@
     <row r="48" spans="1:17" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B48" s="1" t="str">
         <f>[1]Gesamt!B50</f>
-        <v>Sven Köpernick</v>
+        <v>Tim-Peter Blunck</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" s="1">
@@ -5778,7 +5751,7 @@
       </c>
       <c r="L48" s="1">
         <f>[1]Gesamt!D50</f>
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="M48" s="1">
         <f>[1]Gesamt!Y50</f>
@@ -5804,28 +5777,28 @@
     <row r="49" spans="1:17" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B49" s="1" t="str">
         <f>[1]Gesamt!B51</f>
-        <v>Till Greiner-Hiero</v>
+        <v>Torge Bremer</v>
       </c>
       <c r="C49" s="1">
         <v>29</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E49" s="2">
         <v>45861</v>
       </c>
       <c r="F49" s="1">
         <f>[1]Gesamt!C51</f>
-        <v>517</v>
+        <v>0</v>
       </c>
       <c r="G49" s="1">
         <f>[1]Gesamt!X51</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H49" s="1">
         <f>[1]Gesamt!U51</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I49" s="1">
         <f>[1]Gesamt!L51</f>
@@ -5865,25 +5838,22 @@
       </c>
     </row>
     <row r="50" spans="1:17" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A50" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="B50" s="1" t="str">
         <f>[1]Gesamt!B52</f>
-        <v>Tim Sachau</v>
+        <v>Veit Brücker</v>
       </c>
       <c r="C50" s="1">
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E50" s="2">
         <v>45474</v>
       </c>
       <c r="F50" s="1">
         <f>[1]Gesamt!C52</f>
-        <v>1710</v>
+        <v>0</v>
       </c>
       <c r="G50" s="1">
         <f>[1]Gesamt!X52</f>
@@ -5895,7 +5865,7 @@
       </c>
       <c r="I50" s="1">
         <f>[1]Gesamt!L52</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J50" s="1">
         <f>[1]Gesamt!O52</f>
@@ -5933,7 +5903,7 @@
     <row r="51" spans="1:17" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B51" s="1" t="str">
         <f>[1]Gesamt!B53</f>
-        <v>Tim Stratmann</v>
+        <v>Yannik Frahm</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" s="1">
@@ -5962,11 +5932,11 @@
       </c>
       <c r="L51" s="1">
         <f>[1]Gesamt!D53</f>
-        <v>420</v>
+        <v>0</v>
       </c>
       <c r="M51" s="1">
         <f>[1]Gesamt!Y53</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N51" s="1">
         <f>[1]Gesamt!V53</f>
@@ -5974,7 +5944,7 @@
       </c>
       <c r="O51" s="1">
         <f>[1]Gesamt!M53</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P51" s="1">
         <f>[1]Gesamt!P53</f>
@@ -5988,10 +5958,10 @@
     <row r="52" spans="1:17" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B52" s="1" t="str">
         <f>[1]Gesamt!B54</f>
-        <v>Torge Bremer</v>
+        <v>Z1 Alexander Schrinner</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E52" s="2">
         <v>41793</v>
@@ -6022,7 +5992,7 @@
       </c>
       <c r="L52" s="1">
         <f>[1]Gesamt!D54</f>
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="M52" s="1">
         <f>[1]Gesamt!Y54</f>
@@ -6048,7 +6018,7 @@
     <row r="53" spans="1:17" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B53" s="1" t="str">
         <f>[1]Gesamt!B55</f>
-        <v>Veit Brücker</v>
+        <v>Z2 Mirco Maschevsky</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>0</v>
@@ -6082,7 +6052,7 @@
       </c>
       <c r="L53" s="1">
         <f>[1]Gesamt!D55</f>
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="M53" s="1">
         <f>[1]Gesamt!Y55</f>
@@ -6090,7 +6060,7 @@
       </c>
       <c r="N53" s="1">
         <f>[1]Gesamt!V55</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O53" s="1">
         <f>[1]Gesamt!M55</f>
@@ -6108,7 +6078,7 @@
     <row r="54" spans="1:17" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B54" s="1" t="str">
         <f>[1]Gesamt!B56</f>
-        <v>Z1 Joso Jochimsen</v>
+        <v>Z3 Dennis Witt</v>
       </c>
       <c r="E54" s="2">
         <v>45898</v>
@@ -6139,7 +6109,7 @@
       </c>
       <c r="L54" s="1">
         <f>[1]Gesamt!D56</f>
-        <v>198</v>
+        <v>0</v>
       </c>
       <c r="M54" s="1">
         <f>[1]Gesamt!Y56</f>
@@ -6151,7 +6121,7 @@
       </c>
       <c r="O54" s="1">
         <f>[1]Gesamt!M56</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P54" s="1">
         <f>[1]Gesamt!P56</f>
@@ -6163,12 +6133,12 @@
       </c>
     </row>
     <row r="55" spans="1:17" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B55" s="1" t="str">
+      <c r="B55" s="1">
         <f>[1]Gesamt!B57</f>
-        <v>Z2 Lars Heinrich</v>
+        <v>0</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E55" s="2">
         <v>37161</v>
@@ -6199,7 +6169,7 @@
       </c>
       <c r="L55" s="1">
         <f>[1]Gesamt!D57</f>
-        <v>209</v>
+        <v>0</v>
       </c>
       <c r="M55" s="1">
         <f>[1]Gesamt!Y57</f>
@@ -6223,12 +6193,12 @@
       </c>
     </row>
     <row r="56" spans="1:17" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B56" s="1" t="str">
+      <c r="B56" s="1">
         <f>[1]Gesamt!B58</f>
-        <v>Z3 Jason Hannemann</v>
+        <v>0</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" s="1">
@@ -6257,7 +6227,7 @@
       </c>
       <c r="L56" s="1">
         <f>[1]Gesamt!D58</f>
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="M56" s="1">
         <f>[1]Gesamt!Y58</f>
@@ -6281,23 +6251,23 @@
       </c>
     </row>
     <row r="57" spans="1:17" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B57" s="1" t="str">
+      <c r="B57" s="1">
         <f>[1]Gesamt!B59</f>
-        <v>Z4 Pascal Diedrichsen</v>
+        <v>0</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E57" s="2">
         <v>41275</v>
       </c>
       <c r="F57" s="1">
         <f>[1]Gesamt!C59</f>
-        <v>333</v>
+        <v>0</v>
       </c>
       <c r="G57" s="1">
         <f>[1]Gesamt!X59</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H57" s="1">
         <f>[1]Gesamt!U59</f>
